--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
     <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -782,7 +830,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -814,16 +862,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920051</v>
+        <v>21330051920037</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -833,6 +881,144 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920053</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920062</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920133</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920051</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -85,33 +85,36 @@
     <t>TLAXCALTECALT</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>NOYOLA</t>
   </si>
   <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
@@ -121,16 +124,19 @@
     <t>KARLA JAZMIN</t>
   </si>
   <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -830,7 +836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -868,10 +874,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -891,10 +897,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -917,7 +923,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -931,7 +937,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920132</v>
+        <v>20330051920134</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -940,7 +946,7 @@
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -954,19 +960,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920133</v>
+        <v>20330051920137</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -977,47 +983,70 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920137</v>
+        <v>21330051920051</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920051</v>
+        <v>20330051920132</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -85,36 +85,42 @@
     <t>TLAXCALTECALT</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
@@ -124,19 +130,22 @@
     <t>KARLA JAZMIN</t>
   </si>
   <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
     <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
   </si>
 </sst>
 </file>
@@ -836,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -874,10 +883,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -897,10 +906,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -920,10 +929,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -937,16 +946,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920134</v>
+        <v>20330051920137</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -960,16 +969,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920137</v>
+        <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -989,10 +998,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1012,10 +1021,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1035,10 +1044,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1047,6 +1056,29 @@
         <v>12</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920134</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,6 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>OREA</t>
-  </si>
-  <si>
     <t>TLAXCALTECALT</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
@@ -845,7 +839,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -883,10 +877,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -900,16 +894,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920053</v>
+        <v>21330051920062</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -923,7 +917,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920062</v>
+        <v>20330051920137</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -932,13 +926,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -946,7 +940,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920137</v>
+        <v>20330051920387</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -955,7 +949,7 @@
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -969,7 +963,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920387</v>
+        <v>21330051920051</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -978,21 +972,21 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920051</v>
+        <v>20330051920132</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1001,13 +995,13 @@
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1015,19 +1009,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -1038,47 +1032,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920134</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -79,67 +79,28 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>NOYOLA</t>
   </si>
   <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
+    <t>ESMERALDA</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
   </si>
 </sst>
 </file>
@@ -540,10 +501,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -552,7 +513,7 @@
         <v>73.17</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -566,10 +527,10 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>26</v>
@@ -578,7 +539,7 @@
         <v>74.29000000000001</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -592,10 +553,10 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>24</v>
@@ -604,7 +565,7 @@
         <v>68.56999999999999</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -657,16 +618,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.48999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -680,16 +644,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -703,16 +670,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -765,19 +735,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,19 +761,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,19 +787,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>68.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -877,10 +847,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -894,22 +864,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920062</v>
+        <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -917,16 +887,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920137</v>
+        <v>20330051920132</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -936,121 +906,6 @@
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920387</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920051</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920132</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920134</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,12 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -88,6 +94,9 @@
     <t>DEL ROSARIO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -95,6 +104,12 @@
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>ESMERALDA</t>
@@ -809,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -847,10 +862,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -864,16 +879,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920126</v>
+        <v>20330051920119</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -887,16 +902,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920132</v>
+        <v>20330051920119</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -906,6 +921,98 @@
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920151</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920151</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,48 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -516,10 +474,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -528,7 +486,7 @@
         <v>73.17</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -633,10 +591,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>33</v>
@@ -645,7 +603,7 @@
         <v>80.48999999999999</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -750,19 +708,19 @@
         <v>41</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>80.48999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -779,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -805,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -854,167 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920037</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920119</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920119</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920151</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920151</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920126</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920132</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
